--- a/order_generation/docs/empty_base_template.xlsx
+++ b/order_generation/docs/empty_base_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cheng\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cheng\Desktop\amazon_order\order_generation\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35E47DD3-F7EF-415E-8E17-82D6B623DB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFE6F2F-47F4-43F7-826A-B35EA70424E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,73 +33,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>供货商：</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>电话：</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>联系人：</t>
-    </r>
-  </si>
-  <si>
-    <t>产品图片</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>数量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>个</t>
-    </r>
-  </si>
-  <si>
     <t>单价</t>
   </si>
   <si>
@@ -259,63 +192,63 @@
       <t>0574-27889655
 sales@hair-brushes.com    lucky@jsiu.com</t>
     </r>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Logo</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>色卡</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>订单号</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>以上价格含税运含包装</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>进仓地址：</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>日期</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>订单安排人</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>产品编号</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>付款方式:</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>交货时间:</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>箱规:</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>产前确认样:</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>出货样:</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>注意事项:</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -330,7 +263,7 @@
       </rPr>
       <t>）</t>
     </r>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -345,6 +278,7 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -359,6 +293,7 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -373,6 +308,7 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -387,6 +323,7 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -401,6 +338,7 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -415,6 +353,7 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -429,6 +368,7 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -443,6 +383,7 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -457,6 +398,7 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -471,6 +413,7 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -485,18 +428,79 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电话：</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>联系人：</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品图片</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>供货商：</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="\¥#,##0.00;\¥\-#,##0.00"/>
-    <numFmt numFmtId="177" formatCode="0&quot;PCS&quot;"/>
-  </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -532,12 +536,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -595,20 +593,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -625,45 +612,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="14"/>
       <name val="宋体"/>
       <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -681,7 +632,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -705,19 +656,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -727,13 +665,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -754,49 +689,31 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="26" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -805,98 +722,33 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="27" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1155,438 +1007,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>2196</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="815340" y="5061585"/>
-          <a:ext cx="556260" cy="1905"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="1">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>340360</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2298700</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>5249</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="email"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1102360" y="5061585"/>
-          <a:ext cx="1958340" cy="5080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="1">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>340360</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2298700</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>5249</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="email"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1102360" y="5061585"/>
-          <a:ext cx="1958340" cy="5080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="1">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>2196</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="815340" y="5061585"/>
-          <a:ext cx="556260" cy="1905"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="1">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>95675</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>132308</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>2</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Bildobjekt 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="2403475" y="3515360"/>
-          <a:ext cx="0" cy="3091815"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>139701</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>127077</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>2683</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Bildobjekt 53">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="2421255" y="3541395"/>
-          <a:ext cx="3175" cy="3042920"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>129540</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>4144</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Bildobjekt 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="2440940" y="3559810"/>
-          <a:ext cx="4445" cy="3007360"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>128024</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1272</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Bildobjekt 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="2413000" y="3530600"/>
-          <a:ext cx="1270" cy="3062605"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>128024</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1272</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Bildobjekt 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="2413000" y="3530600"/>
-          <a:ext cx="1270" cy="3062605"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>16</xdr:row>
@@ -1644,7 +1064,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>45719</xdr:rowOff>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1692,7 +1112,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>107577</xdr:rowOff>
+      <xdr:rowOff>96370</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1740,7 +1160,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>107577</xdr:rowOff>
+      <xdr:rowOff>96370</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1777,123 +1197,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3008705" cy="4144"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Bildobjekt 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AD3E6E0-5473-4453-A180-8211F8D6B3C1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="2442081" y="3535884"/>
-          <a:ext cx="4144" cy="3008705"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3064339" cy="1272"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Bildobjekt 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{336B41A0-1306-4EEA-9B35-4C4FDBC06684}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="2414184" y="3506631"/>
-          <a:ext cx="1272" cy="3064339"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3064339" cy="1272"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Bildobjekt 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5AC8793-C4D4-4741-9E49-DB5AB3B70AF4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="2414184" y="3506631"/>
-          <a:ext cx="1272" cy="3064339"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -2595,423 +1898,423 @@
     <col min="3" max="3" width="35.85546875" style="7" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" style="7" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="7" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" style="7" customWidth="1"/>
     <col min="8" max="8" width="17.28515625" style="7" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="31.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+    </row>
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-    </row>
-    <row r="2" spans="1:8" ht="31.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="16"/>
+    </row>
+    <row r="6" spans="1:8" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-    </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="F6" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="20"/>
-    </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+      <c r="G6" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="23"/>
-      <c r="H5" s="20"/>
-    </row>
-    <row r="6" spans="1:8" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="26"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" s="2" customFormat="1" ht="100.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="26"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" s="2" customFormat="1" ht="100.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="26"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="20"/>
     </row>
     <row r="9" spans="1:8" s="2" customFormat="1" ht="100.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="26"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="32">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19">
         <f>SUM(D7:D9)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30">
+      <c r="E10" s="19"/>
+      <c r="F10" s="19">
         <f>SUM(F7:F8)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="33"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="21"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="34" t="s">
+      <c r="A11" s="21"/>
+      <c r="B11" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+    </row>
+    <row r="12" spans="1:8" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+    </row>
+    <row r="13" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="25"/>
+    </row>
+    <row r="14" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-    </row>
-    <row r="12" spans="1:8" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="58" t="s">
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+    </row>
+    <row r="15" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-    </row>
-    <row r="13" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="58" t="s">
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+    </row>
+    <row r="16" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+    </row>
+    <row r="17" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+    </row>
+    <row r="18" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+    </row>
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="40"/>
-    </row>
-    <row r="14" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58" t="s">
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+    </row>
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-    </row>
-    <row r="15" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="58" t="s">
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+    </row>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A21" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-    </row>
-    <row r="16" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="58" t="s">
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+    </row>
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A22" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-    </row>
-    <row r="17" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="58" t="s">
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+    </row>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A23" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="47"/>
-    </row>
-    <row r="18" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="57" t="s">
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+    </row>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-    </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="49" t="s">
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-    </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="49" t="s">
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-    </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="49" t="s">
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+    </row>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A27" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-    </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="49" t="s">
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+    </row>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A28" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="49"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-    </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="s">
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+    </row>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A29" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-    </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="49" t="s">
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+    </row>
+    <row r="30" spans="1:9" s="5" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A30" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="5"/>
-    </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48"/>
-    </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="48"/>
-    </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="49"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="48"/>
-    </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="49"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="54"/>
-    </row>
-    <row r="30" spans="1:9" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="49"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="55"/>
-    </row>
-    <row r="31" spans="1:9" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A31" s="47"/>
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="54"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+    </row>
+    <row r="31" spans="1:9" s="5" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A31" s="25"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
     </row>
     <row r="32" spans="1:9" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="47"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="56"/>
-    </row>
-    <row r="33" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="47"/>
-      <c r="B33" s="47"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="56"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+    </row>
+    <row r="33" spans="1:8" s="5" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34"/>
@@ -3021,7 +2324,7 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34"/>
-      <c r="H34" s="15"/>
+      <c r="H34" s="14"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35"/>
@@ -3061,7 +2364,7 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38"/>
-      <c r="H38" s="15"/>
+      <c r="H38" s="14"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39"/>
@@ -3104,8 +2407,8 @@
       <c r="H42"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="13"/>
+      <c r="A43" s="10"/>
+      <c r="B43" s="12"/>
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
@@ -3114,8 +2417,8 @@
       <c r="H43"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
@@ -3124,8 +2427,8 @@
       <c r="H44"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
       <c r="C45"/>
       <c r="D45"/>
       <c r="E45"/>
@@ -3134,8 +2437,8 @@
       <c r="H45"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
-      <c r="B46" s="11"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
       <c r="C46"/>
       <c r="D46"/>
       <c r="E46"/>
@@ -3144,8 +2447,8 @@
       <c r="H46"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
       <c r="C47"/>
       <c r="D47"/>
       <c r="E47"/>
@@ -3154,8 +2457,8 @@
       <c r="H47"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
       <c r="C48"/>
       <c r="D48"/>
       <c r="E48"/>
@@ -3164,8 +2467,8 @@
       <c r="H48"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
       <c r="C49"/>
       <c r="D49"/>
       <c r="E49"/>
@@ -3174,8 +2477,8 @@
       <c r="H49"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
       <c r="C50"/>
       <c r="D50"/>
       <c r="E50"/>
@@ -3184,8 +2487,8 @@
       <c r="H50"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
+      <c r="A51" s="10"/>
+      <c r="B51" s="10"/>
       <c r="C51"/>
       <c r="D51"/>
       <c r="E51"/>
@@ -3194,8 +2497,8 @@
       <c r="H51"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
+      <c r="A52" s="10"/>
+      <c r="B52" s="10"/>
       <c r="C52"/>
       <c r="D52"/>
       <c r="E52"/>
@@ -3204,8 +2507,8 @@
       <c r="H52"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
       <c r="C53"/>
       <c r="D53"/>
       <c r="E53"/>
@@ -3214,8 +2517,8 @@
       <c r="H53"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
+      <c r="A54" s="10"/>
+      <c r="B54" s="10"/>
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54"/>
@@ -3224,8 +2527,8 @@
       <c r="H54"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
+      <c r="A55" s="10"/>
+      <c r="B55" s="10"/>
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
@@ -3234,8 +2537,8 @@
       <c r="H55"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
+      <c r="A56" s="10"/>
+      <c r="B56" s="10"/>
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
@@ -3244,8 +2547,8 @@
       <c r="H56"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
+      <c r="A57" s="10"/>
+      <c r="B57" s="10"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
@@ -3254,8 +2557,8 @@
       <c r="H57"/>
     </row>
     <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
+      <c r="A58" s="10"/>
+      <c r="B58" s="10"/>
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58"/>
@@ -3264,8 +2567,8 @@
       <c r="H58"/>
     </row>
     <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
+      <c r="A59" s="10"/>
+      <c r="B59" s="10"/>
       <c r="C59"/>
       <c r="D59"/>
       <c r="E59"/>
@@ -3274,8 +2577,8 @@
       <c r="H59"/>
     </row>
     <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
+      <c r="A60" s="10"/>
+      <c r="B60" s="10"/>
       <c r="C60"/>
       <c r="D60"/>
       <c r="E60"/>
@@ -3284,8 +2587,8 @@
       <c r="H60"/>
     </row>
     <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
       <c r="C61"/>
       <c r="D61"/>
       <c r="E61"/>
@@ -3294,8 +2597,8 @@
       <c r="H61"/>
     </row>
     <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
+      <c r="A62" s="10"/>
+      <c r="B62" s="10"/>
       <c r="C62"/>
       <c r="D62"/>
       <c r="E62"/>
@@ -3304,8 +2607,8 @@
       <c r="H62"/>
     </row>
     <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
+      <c r="A63" s="10"/>
+      <c r="B63" s="10"/>
       <c r="C63"/>
       <c r="D63"/>
       <c r="E63"/>
@@ -3314,8 +2617,8 @@
       <c r="H63"/>
     </row>
     <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
+      <c r="A64" s="10"/>
+      <c r="B64" s="10"/>
       <c r="C64"/>
       <c r="D64"/>
       <c r="E64"/>
@@ -3324,8 +2627,8 @@
       <c r="H64"/>
     </row>
     <row r="65" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
+      <c r="A65" s="10"/>
+      <c r="B65" s="10"/>
       <c r="C65"/>
       <c r="D65"/>
       <c r="E65"/>
@@ -3334,8 +2637,8 @@
       <c r="H65"/>
     </row>
     <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
+      <c r="A66" s="10"/>
+      <c r="B66" s="10"/>
       <c r="C66"/>
       <c r="D66"/>
       <c r="E66"/>
@@ -3344,8 +2647,8 @@
       <c r="H66"/>
     </row>
     <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A67" s="11"/>
-      <c r="B67" s="13"/>
+      <c r="A67" s="10"/>
+      <c r="B67" s="12"/>
       <c r="C67"/>
       <c r="D67"/>
       <c r="E67"/>
@@ -3365,29 +2668,29 @@
     </row>
     <row r="69" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A69"/>
-      <c r="B69" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" s="10"/>
-      <c r="G69" s="15"/>
+      <c r="B69" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F69" s="9"/>
+      <c r="G69" s="14"/>
       <c r="H69"/>
     </row>
     <row r="70" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A70"/>
-      <c r="B70" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" s="14"/>
+      <c r="B70" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F70" s="13"/>
       <c r="G70"/>
       <c r="H70"/>
     </row>
@@ -3489,7 +2792,7 @@
       <c r="E80"/>
       <c r="F80"/>
       <c r="G80"/>
-      <c r="H80" s="15"/>
+      <c r="H80" s="14"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81"/>
@@ -3560,23 +2863,11 @@
       <c r="H88"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.78740157480314998" bottom="0.59055118110236204" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="65" orientation="portrait" horizontalDpi="360" verticalDpi="360"/>

--- a/order_generation/docs/empty_base_template.xlsx
+++ b/order_generation/docs/empty_base_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cheng\Desktop\amazon_order\order_generation\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFE6F2F-47F4-43F7-826A-B35EA70424E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1D8186-1AB7-44B3-8237-69ED239006C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -668,7 +668,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -738,13 +738,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1905,16 +1908,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="31.5" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
@@ -1995,33 +1998,33 @@
       <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" s="2" customFormat="1" ht="100.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
       <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" s="2" customFormat="1" ht="100.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
       <c r="H8" s="20"/>
     </row>
     <row r="9" spans="1:8" s="2" customFormat="1" ht="100.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
